--- a/inst/extdata/default_files.xlsx
+++ b/inst/extdata/default_files.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Work\TT_Backup2\TADACommunityHub\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/sheila_saia_tetratech_com/Documents/Documents/github/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06581A83-2530-4037-BDFD-D3F7BAD9AD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{06581A83-2530-4037-BDFD-D3F7BAD9AD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28152D43-7FB5-478A-BF0F-6DA4B07EAB4A}"/>
   <bookViews>
-    <workbookView xWindow="12285" yWindow="15" windowWidth="9315" windowHeight="12765" xr2:uid="{B640AF5E-9189-491C-882A-901B5AA8762B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B640AF5E-9189-491C-882A-901B5AA8762B}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -166,14 +166,14 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="新細明體"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -207,7 +207,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -223,7 +223,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -540,13 +540,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5264381A-6059-463E-BFBC-74943D3E850C}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.46484375" customWidth="1"/>
+    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -557,7 +557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -579,7 +579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -590,7 +590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -601,7 +601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -612,7 +612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -623,7 +623,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -634,7 +634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -645,7 +645,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -656,7 +656,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -667,7 +667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -678,7 +678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>37</v>
       </c>
